--- a/data/valuations/SLP/SLP_modelo_valoracion.xlsx
+++ b/data/valuations/SLP/SLP_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.017</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.002999999999999999</v>
+        <v>0.033</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.013</v>
+        <v>0.05</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.023</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.002999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.002699999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.002399999999999999</v>
+        <v>0.048</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.002099999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.0018</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.04699999999999999</v>
+        <v>-0.022</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.03699999999999999</v>
+        <v>-0.001999999999999995</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.027</v>
+        <v>0.018</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.01699999999999999</v>
+        <v>0.03800000000000001</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.006999999999999992</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="11">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.7210288075637667</v>
+        <v>0.7110288075637667</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.7210288075637667</v>
+        <v>0.7110288075637667</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.7210288075637667</v>
+        <v>0.7110288075637667</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.7210288075637667</v>
+        <v>0.7110288075637667</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.7210288075637667</v>
+        <v>0.7110288075637667</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.6810288075637667</v>
+        <v>0.6910288075637667</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6810288075637667</v>
+        <v>0.6910288075637667</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6810288075637667</v>
+        <v>0.6910288075637667</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.6810288075637667</v>
+        <v>0.6910288075637667</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.6810288075637667</v>
+        <v>0.6910288075637667</v>
       </c>
     </row>
     <row r="18">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.4647159859062217</v>
+        <v>0.4697159859062217</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.4647159859062217</v>
+        <v>0.4697159859062217</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.4647159859062217</v>
+        <v>0.4697159859062217</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.4647159859062217</v>
+        <v>0.4697159859062217</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.4647159859062217</v>
+        <v>0.4697159859062217</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.4847159859062217</v>
+        <v>0.4797159859062217</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.4847159859062217</v>
+        <v>0.4797159859062217</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4847159859062217</v>
+        <v>0.4797159859062217</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4847159859062217</v>
+        <v>0.4797159859062217</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.4847159859062217</v>
+        <v>0.4797159859062217</v>
       </c>
     </row>
     <row r="23">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.08105940667402126</v>
+        <v>0.07605940667402125</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.08105940667402126</v>
+        <v>0.07605940667402125</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.08105940667402126</v>
+        <v>0.07605940667402125</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.08105940667402126</v>
+        <v>0.07605940667402125</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.08105940667402126</v>
+        <v>0.07605940667402125</v>
       </c>
     </row>
     <row r="28">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.06345512973621976</v>
+        <v>0.06657687869500786</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.06345512973621976</v>
+        <v>0.06657687869500786</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.06345512973621976</v>
+        <v>0.06657687869500786</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.06345512973621976</v>
+        <v>0.06657687869500786</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.06345512973621976</v>
+        <v>0.06657687869500786</v>
       </c>
     </row>
     <row r="32">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1318</v>
+        <v>0.1218</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>0.6</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="D23" s="12" t="n">
         <v>0.49</v>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>12.12</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="4">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="K21" s="8">
-        <f>K12*$C$16</f>
+        <f>K8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/12.12-1</f>
+        <f>C33/11.42-1</f>
         <v/>
       </c>
     </row>
@@ -3727,27 +3727,27 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>9x</t>
+          <t>11x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>11x</t>
+          <t>13x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>13x</t>
+          <t>15x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>15x</t>
+          <t>17x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>17x</t>
+          <t>19x</t>
         </is>
       </c>
     </row>
@@ -3756,23 +3756,23 @@
         <v>0.0818</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*9/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*11/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*11/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*13/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*13/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*15/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*15/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*17/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*17/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*19/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3781,23 +3781,23 @@
         <v>0.09179999999999999</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*9/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*11/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*11/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*13/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*13/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*15/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*15/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*17/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*17/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*19/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3806,23 +3806,23 @@
         <v>0.1018</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*9/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*11/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*11/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*13/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*13/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*15/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*15/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*17/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*17/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*19/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3831,23 +3831,23 @@
         <v>0.1118</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*9/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*11/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*11/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*13/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*13/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*15/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*15/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*17/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*17/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*19/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3856,23 +3856,23 @@
         <v>0.1218</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*9/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*11/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*11/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*13/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*13/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*15/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*15/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*17/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*17/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*19/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3881,23 +3881,23 @@
         <v>0.1318</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*9/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*11/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*11/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*13/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*13/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*15/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*15/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*17/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*17/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*19/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3906,23 +3906,23 @@
         <v>0.1418</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*9/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*11/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*11/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*13/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*13/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*15/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*15/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*17/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*17/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*19/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/SLP/SLP_modelo_valoracion.xlsx
+++ b/data/valuations/SLP/SLP_modelo_valoracion.xlsx
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="D23" s="12" t="n">
         <v>0.49</v>
